--- a/order_generation/PO_import_filled/PO_import_test.xlsx
+++ b/order_generation/PO_import_filled/PO_import_test.xlsx
@@ -856,7 +856,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>宁波泰丰机械有限公司</t>
+          <t>宁波瑾秀制刷科技有限公司</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -898,7 +898,7 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>17-A1KN-KJGW</t>
+          <t>EEHB-NBB</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
@@ -910,13 +910,15 @@
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>5.14</v>
+        <v>12.89</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>白色针+黑色（TPR）胶皮参考denman样品，手柄571U透明弹性漆，背面印白色logo 包装方式：纸卡包装系扎带，包装背面贴fba不干胶，套opp袋，注意单箱不要超过100个</t>
+          <t>手柄表面电镀处理尽量光亮，黑色手柄做防静电处理。
+气垫颜色（打样确认色），植猪鬃毛，梳针颜色黑色防静电，植0.8 mm细尼龙针染头和梳针颜色一致，染头尽量偏小（视觉效果染头和梳针一体）梳针做防静电处理。
+LOGO：ellen evyse 颜色印金，注意LOGO颜色光泽度，与2025.11.20签样一致</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
@@ -924,17 +926,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test-2</t>
+          <t>test-1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>XX印刷厂</t>
+          <t>宁波瑾秀制刷科技有限公司</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -976,7 +978,7 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>17-A1KN-KJGW-1</t>
+          <t>EEHB-NBB-4</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
@@ -988,28 +990,329 @@
         <v>1</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>黑人卷发梳双面印刷哑膜过UV，500g白卡</t>
+          <t>清洁刷，注塑体黑色，植毛黑色尼龙毛，0.7mm直径，长度25mm，定制
+Ellen Evyse滑块logo，产品做哑光，logo处做亮光。需打样再做货</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n"/>
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>test-2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>义乌市一柠饰品有限公司</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>按数量</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>默认仓库</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>EEHB-NBB-1C</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>浅咖色</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="5" t="n"/>
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>test-2</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>义乌市一柠饰品有限公司</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>按数量</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>默认仓库</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>EEHB-NBB-1B</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>黑色</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="5" t="n"/>
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>test-3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>盐城市艳丽工艺品有限公司</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>按数量</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>默认仓库</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>EEHB-NBB-2</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>12*25黑色棘皮绒单面，黑色棉绳，烫金logo</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="5" t="n"/>
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>test-4</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>XX印刷厂</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>按数量</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>默认仓库</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>EEHB-NBB-3</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>猪鬃红色胶皮天地盖礼盒，盖子logo烫金，表面磨砂材质</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>

--- a/order_generation/PO_import_filled/PO_import_test.xlsx
+++ b/order_generation/PO_import_filled/PO_import_test.xlsx
@@ -856,7 +856,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>宁波瑾秀制刷科技有限公司</t>
+          <t>宁波市海曙硕丰塑料五金制品有限公司</t>
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
@@ -898,7 +898,7 @@
       <c r="X3" t="inlineStr"/>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>EEHB-NBB</t>
+          <t>ST1122-1</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr"/>
@@ -907,18 +907,16 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr"/>
       <c r="AE3" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="AF3" t="n">
-        <v>12.89</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="inlineStr"/>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>手柄表面电镀处理尽量光亮，黑色手柄做防静电处理。
-气垫颜色（打样确认色），植猪鬃毛，梳针颜色黑色防静电，植0.8 mm细尼龙针染头和梳针颜色一致，染头尽量偏小（视觉效果染头和梳针一体）梳针做防静电处理。
-LOGO：ellen evyse 颜色印金，注意LOGO颜色光泽度，与2025.11.20签样一致</t>
+          <t>黑色气垫猪鬃手柄：水曲柳手柄棕黑色喷漆双层，喷漆效果参考Moroccooil，形状同寄样。8.5*24.5*1.3，金色移印logoNorsewood。梳面开口严格按照提供线稿，礼盒包装我司提供，胶皮配件我司提供，清洁刷和布袋我司提供，需装配，贴标。</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr"/>
@@ -926,17 +924,17 @@
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>test-1</t>
+          <t>test-2</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>宁波瑾秀制刷科技有限公司</t>
+          <t>和鑫制刷厂</t>
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
@@ -978,7 +976,7 @@
       <c r="X4" t="inlineStr"/>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>EEHB-NBB-4</t>
+          <t>US-RB01-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr"/>
@@ -987,17 +985,16 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr"/>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.64</v>
+        <v>10.8</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="inlineStr"/>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>清洁刷，注塑体黑色，植毛黑色尼龙毛，0.7mm直径，长度25mm，定制
-Ellen Evyse滑块logo，产品做哑光，logo处做亮光。需打样再做货</t>
+          <t>禾木清洁刷清漆，3.1*7.3*1.1 厘米48孔。尼龙刷毛出峰2.5cm，加粗0.7mm，刷子表面和刷面清洁不要有碎屑附着,背后要加印logo Norsewood激光logo,散货</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr"/>
@@ -1005,17 +1002,17 @@
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>test-2</t>
+          <t>test-3</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>义乌市一柠饰品有限公司</t>
+          <t>浙江太平洋纸业</t>
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
@@ -1057,7 +1054,7 @@
       <c r="X5" t="inlineStr"/>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>EEHB-NBB-1C</t>
+          <t>XLZ</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr"/>
@@ -1066,16 +1063,16 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr"/>
       <c r="AE5" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.45</v>
+        <v>0.063</v>
       </c>
       <c r="AG5" t="inlineStr"/>
       <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>浅咖色</t>
+          <t>25*30白底单色logo 28g打字纸</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr"/>
@@ -1083,17 +1080,17 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>test-2</t>
+          <t>test-4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>义乌市一柠饰品有限公司</t>
+          <t>XX印刷厂</t>
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
@@ -1135,7 +1132,7 @@
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>EEHB-NBB-1B</t>
+          <t>TZ</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr"/>
@@ -1144,16 +1141,16 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr"/>
       <c r="AE6" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.45</v>
+        <v>0.05</v>
       </c>
       <c r="AG6" t="inlineStr"/>
       <c r="AH6" t="inlineStr"/>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>黑色</t>
+          <t>圆形品牌logo贴纸</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr"/>
@@ -1161,17 +1158,17 @@
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>test-3</t>
+          <t>test-4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>盐城市艳丽工艺品有限公司</t>
+          <t>XX印刷厂</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
@@ -1213,7 +1210,7 @@
       <c r="X7" t="inlineStr"/>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>EEHB-NBB-2</t>
+          <t>ST1122-4</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr"/>
@@ -1222,16 +1219,16 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr"/>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.37</v>
+        <v>2.93</v>
       </c>
       <c r="AG7" t="inlineStr"/>
       <c r="AH7" t="inlineStr"/>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>12*25黑色棘皮绒单面，黑色棉绳，烫金logo</t>
+          <t>猪鬃木纹天地盖礼盒，盖子logo烫金，表面磨砂材质</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr"/>
@@ -1239,17 +1236,17 @@
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>test-4</t>
+          <t>test-5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>XX印刷厂</t>
+          <t>盐城市艳丽工艺品有限公司</t>
         </is>
       </c>
       <c r="D8" t="inlineStr"/>
@@ -1291,7 +1288,7 @@
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>EEHB-NBB-3</t>
+          <t>SSD</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr"/>
@@ -1300,25 +1297,175 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr"/>
       <c r="AE8" t="n">
-        <v>1</v>
+        <v>1200</v>
       </c>
       <c r="AF8" t="n">
-        <v>3.03</v>
+        <v>1.3</v>
       </c>
       <c r="AG8" t="inlineStr"/>
       <c r="AH8" t="inlineStr"/>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>猪鬃红色胶皮天地盖礼盒，盖子logo烫金，表面磨砂材质</t>
+          <t>15*20黑色棘皮绒单面，黑色棉绳，双色logo，N字母烫金</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="5" t="n"/>
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>test-6</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>宁波瑾秀制刷科技有限公司</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>按数量</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>默认仓库</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>ST1122-2</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>透明尼龙针+猪鬃.深棕色胶皮（TPR）带纹路模具更新（7589C），0.7mm透明尼龙针+猪鬃，棕色染头（7589C）. 包装方式：散货</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="5" t="n"/>
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>test-7</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>宁波市柯莱威电子科技有限公司</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>按数量</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>CNY</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>默认仓库</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>ST1122-5</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="n">
+        <v>1200</v>
+      </c>
+      <c r="AF10" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>清洁刷，注塑体黑色，植毛黑色尼龙毛，0.7mm直径，长度25mm，定制Norsewood滑块logo，产品做哑光，logo处做亮光。</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>

--- a/order_generation/PO_import_filled/PO_import_test.xlsx
+++ b/order_generation/PO_import_filled/PO_import_test.xlsx
@@ -1451,7 +1451,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>宁波市海曙硕丰塑料五金制品有限公司</t>
+          <t>宁波瑾秀制刷科技有限公司</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1481,18 +1481,18 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>ST1122-1</t>
+          <t>Elasticbrush01</t>
         </is>
       </c>
       <c r="AE3" t="n">
-        <v>2222</v>
+        <v>1200</v>
       </c>
       <c r="AF3" t="n">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>黑色气垫猪鬃手柄：水曲柳手柄棕黑色喷漆双层，喷漆效果参考Moroccooil，形状同寄样。8.5*24.5*1.3，金色移印logoNorsewood。梳面开口严格按照提供线稿，礼盒包装我司提供，胶皮配件我司提供，清洁刷和布袋我司提供，需装配，贴标。</t>
+          <t>梳身半降解材料（用新材料防断裂）加麦秸秆5645 C绿色（注意大货注塑颜色，必须与2025.5.30签样一样），尼龙丝0.8mm7529U灰色尼龙丝颜色同beter，棕色 ecoed logo颜色同beter！染头颜色同梳体. 包装方式：白卡盒，卡盒我司供，箱规120/24</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>和鑫制刷厂</t>
+          <t>菲迪印刷</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>宁波品秀美容科技有限公司</t>
+          <t>宁波集秀美容科技有限公司</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -1539,18 +1539,18 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>US-RB01-01</t>
+          <t>EC221-1-1</t>
         </is>
       </c>
       <c r="AE4" t="n">
-        <v>2222</v>
+        <v>1200</v>
       </c>
       <c r="AF4" t="n">
-        <v>10.8</v>
+        <v>0.45</v>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>禾木清洁刷清漆，3.1*7.3*1.1 厘米48孔。尼龙刷毛出峰2.5cm，加粗0.7mm，刷子表面和刷面清洁不要有碎屑附着,背后要加印logo Norsewood激光logo,散货</t>
+          <t>鱼骨梳包装，350g白卡双面印刷，FSC 绿色</t>
         </is>
       </c>
     </row>
@@ -2076,18 +2076,18 @@
     <mergeCell ref="A1:Q1"/>
   </mergeCells>
   <dataValidations count="9">
-    <dataValidation sqref="A1" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="标识号需要是非零正整数"/>
-    <dataValidation sqref="Q2 S2:T2 T3:T1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1"/>
-    <dataValidation sqref="N3 N4:N5 N6 N7:N1048576 Q3:Q1048576 S3:S1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="A1" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" error="标识号需要是非零正整数"/>
+    <dataValidation sqref="Q2 S2:T2 T3:T1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0"/>
+    <dataValidation sqref="N3 N4:N5 N6 N7:N1048576 Q3:Q1048576 S3:S1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"CNY,VND,USD,TRY,THB,SGD,SEK,SAR,PLN,PHP,MYR,MXN,JPY,INR,IDR,HKD,GBP,EUR,CAD,BRL,AUD,AED"</formula1>
     </dataValidation>
-    <dataValidation sqref="A3:A11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" error="标识号需要是非零正整数" type="whole" operator="greaterThan">
+    <dataValidation sqref="A3:A11" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" error="标识号需要是非零正整数" type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
-    <dataValidation sqref="G3:G1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="G3:G1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"月结,现结"</formula1>
     </dataValidation>
-    <dataValidation sqref="L3:L1048576 AB3:AB1048576 AJ3:AJ1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="list">
+    <dataValidation sqref="L3:L1048576 AB3:AB1048576 AJ3:AJ1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="list">
       <formula1>"是,否"</formula1>
     </dataValidation>
     <dataValidation sqref="M3:M5001" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="输入的值有误" error="您输入的值不在下拉框列表内." type="list" errorStyle="information">
@@ -2096,7 +2096,7 @@
     <dataValidation sqref="U3:U1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" errorTitle="输入的值有误" error="您输入的值不在下拉框列表内." type="list" errorStyle="information">
       <formula1>"仓库质检,预检,免检"</formula1>
     </dataValidation>
-    <dataValidation sqref="AC3:AD1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="1" type="whole" operator="greaterThan">
+    <dataValidation sqref="AC3:AD1048576" showDropDown="0" showInputMessage="1" showErrorMessage="1" allowBlank="0" type="whole" operator="greaterThan">
       <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
